--- a/E/DU2AMKT.xlsx
+++ b/E/DU2AMKT.xlsx
@@ -11,15 +11,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="13">
   <si>
     <t/>
   </si>
   <si>
-    <t>20138236</t>
-  </si>
-  <si>
-    <t>CHEETOS JG BKR 120 G</t>
+    <t>20072194</t>
+  </si>
+  <si>
+    <t>MAITOS S.BLDO 140 G</t>
   </si>
   <si>
     <t>DU2AMKT</t>
@@ -28,16 +28,28 @@
     <t>1</t>
   </si>
   <si>
+    <t>RT,(E-3B)</t>
+  </si>
+  <si>
+    <t>20072195</t>
+  </si>
+  <si>
+    <t>MAITOS JG BBQ 140 G</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>20140185</t>
+  </si>
+  <si>
+    <t>SQ CHKY MINIS 10X8 G</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>RT,(E-1B)</t>
-  </si>
-  <si>
-    <t>20138230</t>
-  </si>
-  <si>
-    <t>DORITOS JG BKR 120 G</t>
-  </si>
-  <si>
-    <t>2</t>
   </si>
 </sst>
 </file>
@@ -430,7 +442,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -499,6 +511,26 @@
         <v>5</v>
       </c>
     </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/E/DU2AMKT.xlsx
+++ b/E/DU2AMKT.xlsx
@@ -16,10 +16,10 @@
     <t/>
   </si>
   <si>
-    <t>20072194</t>
-  </si>
-  <si>
-    <t>MAITOS S.BLDO 140 G</t>
+    <t>10036957</t>
+  </si>
+  <si>
+    <t>HAPPYTOS HIJAU 140 G</t>
   </si>
   <si>
     <t>DU2AMKT</t>
@@ -28,22 +28,22 @@
     <t>1</t>
   </si>
   <si>
-    <t>RT,(E-3B)</t>
-  </si>
-  <si>
-    <t>20072195</t>
-  </si>
-  <si>
-    <t>MAITOS JG BBQ 140 G</t>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
+    <t>20098166</t>
+  </si>
+  <si>
+    <t>HAPPYTOS J.BKR 140 G</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
-    <t>20140185</t>
-  </si>
-  <si>
-    <t>SQ CHKY MINIS 10X8 G</t>
+    <t>20135312</t>
+  </si>
+  <si>
+    <t>WOW SPAGETI CB 80 G</t>
   </si>
   <si>
     <t>3</t>
